--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260904.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
